--- a/artfynd/A 6223-2020 artfynd.xlsx
+++ b/artfynd/A 6223-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6223-2020 artfynd.xlsx
+++ b/artfynd/A 6223-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12588,6 +12588,117 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>122650832</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Sotebubäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>568865</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6991600</v>
+      </c>
+      <c r="S107" t="n">
+        <v>20</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6223-2020 artfynd.xlsx
+++ b/artfynd/A 6223-2020 artfynd.xlsx
@@ -12593,7 +12593,7 @@
         <v>122650832</v>
       </c>
       <c r="B107" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
